--- a/quarto/RemainingNaturalHabitat_and_Loss_formatted.xlsx
+++ b/quarto/RemainingNaturalHabitat_and_Loss_formatted.xlsx
@@ -382,7 +382,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Recent Loss Km2 (1990-2022)</t>
+          <t>Recent loss 1990 to 2022 (km²)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
